--- a/analysis/tables/gpt-neo-2.7B.xlsx
+++ b/analysis/tables/gpt-neo-2.7B.xlsx
@@ -536,27 +536,27 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8386400008693096</v>
+        <v>0.6094117339650319</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1641984375980532</v>
+        <v>-0.07474350417199374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>y = 0.839x - 0.164</t>
+          <t>y = 0.609x - 0.075</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.8256183584309909</v>
+        <v>0.825618358430992</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07320343774613458</v>
+        <v>0.07320343774613459</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1957913257510373</v>
+        <v>0.122648613418859</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6744415632712564</v>
+        <v>0.5346682297930382</v>
       </c>
       <c r="K3" t="n">
         <v>0.1344496767499455</v>
@@ -577,27 +577,27 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8333225780816644</v>
+        <v>0.607843265798543</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.08112386611094255</v>
+        <v>-0.06911617627998626</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>y = 0.833x - 0.081</t>
+          <t>y = 0.608x - 0.069</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.8497227725840172</v>
+        <v>0.8293843650167247</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07233005170190364</v>
+        <v>0.07306698234117925</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09734989576028567</v>
+        <v>0.1137072337047054</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7521987119707219</v>
+        <v>0.5387270895185567</v>
       </c>
       <c r="K4" t="n">
         <v>0.1344496767499455</v>
